--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112C2525-684A-4338-9BC5-7F5708B8373E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323E631E-942D-4FE1-AB97-415C44420B19}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -47,68 +42,74 @@
     <t>None</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>EndDate__c</t>
-  </si>
-  <si>
-    <t>AccountSource__c</t>
-  </si>
-  <si>
     <t>Automation Account</t>
   </si>
   <si>
-    <t>AgencyFund__c</t>
-  </si>
-  <si>
     <t>Automation Fund</t>
   </si>
   <si>
-    <t>AccountType__c</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>CostCategory__c</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>AppropriationBalance__c</t>
-  </si>
-  <si>
     <t>Funding Source Description</t>
   </si>
   <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>Automation Runtime Funding Source</t>
   </si>
   <si>
     <t>Automation Runtime Funding Account</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldAppropriationBalance__c</t>
+  </si>
+  <si>
+    <t>fieldAccountSource__c</t>
+  </si>
+  <si>
+    <t>fieldAgencyFund__c</t>
+  </si>
+  <si>
+    <t>fieldAccountType__c</t>
+  </si>
+  <si>
+    <t>fieldCostCategory__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -140,6 +141,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,13 +457,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,34 +474,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -514,13 +516,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,12 +533,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>3650</v>
@@ -550,13 +552,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.3046875" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,33 +569,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C4">
@@ -609,13 +611,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.53515625" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,70 +628,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B36C0-C33E-4941-B8F4-FA9D379E4EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC96A96-E9D6-4E7D-98E5-25AD90BF0637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>Funding Source Description</t>
   </si>
   <si>
@@ -92,24 +89,6 @@
     <t>fieldTitle__c</t>
   </si>
   <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldAppropriationBalance__c</t>
-  </si>
-  <si>
-    <t>fieldAccountSource__c</t>
-  </si>
-  <si>
-    <t>fieldAgencyFund__c</t>
-  </si>
-  <si>
-    <t>fieldAccountType__c</t>
-  </si>
-  <si>
-    <t>fieldCostCategory__c</t>
-  </si>
-  <si>
     <t>fieldGrant__c</t>
   </si>
   <si>
@@ -123,6 +102,27 @@
   </si>
   <si>
     <t>Federal</t>
+  </si>
+  <si>
+    <t>AppropriationBalance__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>AccountSource__c</t>
+  </si>
+  <si>
+    <t>AgencyFund__c</t>
+  </si>
+  <si>
+    <t>AccountType__c</t>
+  </si>
+  <si>
+    <t>CostCategory__c</t>
+  </si>
+  <si>
+    <t>Contractual</t>
   </si>
 </sst>
 </file>
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -204,7 +204,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -525,13 +524,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,18 +541,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -564,7 +563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -584,13 +583,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,23 +600,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -632,13 +631,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,37 +648,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
@@ -691,13 +690,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,70 +707,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>20</v>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
+      <c r="B5" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -783,13 +782,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,37 +799,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>28</v>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -841,12 +840,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,23 +856,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -887,7 +886,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BackWardCompatibility_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B36C0-C33E-4941-B8F4-FA9D379E4EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48664F6C-EBD6-4174-9F6F-9CBE70B23C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -50,16 +50,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
     <t>Overview</t>
-  </si>
-  <si>
-    <t>EndDate__c</t>
   </si>
   <si>
     <t>Automation Account</t>
@@ -129,19 +120,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="9"/>
@@ -196,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -204,10 +189,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,13 +508,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,34 +525,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -584,13 +567,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,23 +584,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -632,13 +615,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,37 +632,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>10000000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -691,13 +674,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,70 +691,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C3">
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C7" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -783,13 +766,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,37 +783,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>28</v>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -841,12 +824,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,23 +840,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -887,7 +870,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC96A96-E9D6-4E7D-98E5-25AD90BF0637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096CC420-333B-4FA9-A310-090E5556D56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -524,13 +524,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -552,7 +552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -563,7 +563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -583,13 +583,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,7 +600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -611,7 +611,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -631,13 +631,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -659,7 +659,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -690,13 +690,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -718,7 +718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -729,7 +729,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -740,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -762,7 +762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -782,13 +782,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -810,7 +810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -821,7 +821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -840,12 +840,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -867,7 +867,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -886,7 +886,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096CC420-333B-4FA9-A310-090E5556D56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F951F5A-AFE4-464D-AB82-C6E7A75B9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -80,27 +80,12 @@
     <t>Automation Runtime Funding Account</t>
   </si>
   <si>
-    <t>fieldEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
-    <t>fieldGrant__c</t>
-  </si>
-  <si>
     <t>Poonam17420</t>
   </si>
   <si>
     <t>Automation Runtime External Funding Source</t>
   </si>
   <si>
-    <t>fieldType__c</t>
-  </si>
-  <si>
     <t>Federal</t>
   </si>
   <si>
@@ -123,6 +108,12 @@
   </si>
   <si>
     <t>Contractual</t>
+  </si>
+  <si>
+    <t>Grant__c</t>
+  </si>
+  <si>
+    <t>Type__c</t>
   </si>
 </sst>
 </file>
@@ -227,9 +218,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -267,7 +258,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -373,7 +364,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -515,7 +506,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -524,13 +515,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -552,7 +543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -563,7 +554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -583,13 +574,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,7 +591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -611,7 +602,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -631,13 +622,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -659,23 +650,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>10000000</v>
@@ -690,13 +681,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -718,7 +709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -729,45 +720,45 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -782,13 +773,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,37 +790,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -840,12 +831,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,23 +847,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -886,7 +877,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F951F5A-AFE4-464D-AB82-C6E7A75B9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0D3A70-8D95-4C70-A5FE-1E8CC8549F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Funding Account Edition" sheetId="4" r:id="rId4"/>
     <sheet name="External_fs_Creation" sheetId="5" r:id="rId5"/>
     <sheet name="External_FS_Edition" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -794,7 +793,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
@@ -805,7 +804,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -816,7 +815,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -872,13 +871,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0D3A70-8D95-4C70-A5FE-1E8CC8549F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594FCF2-C033-4012-815B-05FAE24C3F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -217,9 +217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +257,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +363,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -573,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -601,7 +601,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -621,13 +621,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -649,7 +649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -660,7 +660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -680,13 +680,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -708,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -719,7 +719,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -730,7 +730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -741,7 +741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -752,7 +752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -772,13 +772,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,7 +800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -811,7 +811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -830,12 +830,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -857,7 +857,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594FCF2-C033-4012-815B-05FAE24C3F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1E31E-D4CC-46DF-B58D-F1C9640597A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>Automation Runtime Funding Account</t>
   </si>
   <si>
-    <t>Poonam17420</t>
-  </si>
-  <si>
     <t>Automation Runtime External Funding Source</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Type__c</t>
+  </si>
+  <si>
+    <t>Poonam17420105333</t>
   </si>
 </sst>
 </file>
@@ -217,9 +217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +257,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +363,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -573,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -601,7 +601,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -621,13 +621,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -649,23 +649,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>10000000</v>
@@ -680,13 +680,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -708,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -719,45 +719,45 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -772,13 +772,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -797,29 +797,29 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -830,12 +830,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -857,7 +857,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1E31E-D4CC-46DF-B58D-F1C9640597A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CACE051-337A-47A4-842D-B8779DF79EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -217,9 +217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +257,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +363,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -573,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -601,7 +601,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -621,13 +621,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -649,7 +649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -660,7 +660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -680,13 +680,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -708,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -719,7 +719,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -730,7 +730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -741,7 +741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -752,7 +752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -772,13 +772,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,7 +800,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -811,7 +811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -830,12 +830,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -857,7 +857,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CACE051-337A-47A4-842D-B8779DF79EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C99E8B-6238-4FDC-AEB0-78A5C20AE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <t>Type__c</t>
   </si>
   <si>
-    <t>Poonam17420105333</t>
+    <t>Automation Grantee Grant</t>
   </si>
 </sst>
 </file>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -573,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -601,7 +601,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -621,13 +621,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -649,7 +649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -660,7 +660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -680,13 +680,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -708,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -719,7 +719,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -730,7 +730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -741,7 +741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -752,7 +752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -772,13 +772,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,18 +800,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -830,12 +830,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -857,7 +857,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B36C0-C33E-4941-B8F4-FA9D379E4EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="External_FS_Edition" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,27 +61,12 @@
     <t>EndDate__c</t>
   </si>
   <si>
-    <t>Automation Account</t>
-  </si>
-  <si>
-    <t>Automation Fund</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>Funding Source Description</t>
-  </si>
-  <si>
-    <t>Automation Runtime Funding Source</t>
-  </si>
-  <si>
-    <t>Automation Runtime Funding Account</t>
-  </si>
-  <si>
     <t>fieldEndDate__c</t>
   </si>
   <si>
@@ -124,11 +108,23 @@
   <si>
     <t>Federal</t>
   </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Department execution details</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Fund</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -523,7 +519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -550,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -582,7 +578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -605,8 +601,8 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2">
         <v>3650</v>
@@ -616,8 +612,8 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+      <c r="B3" t="s">
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -630,11 +626,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -654,10 +650,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>10000000</v>
@@ -676,10 +672,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -713,7 +709,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -724,7 +720,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>2650</v>
@@ -735,10 +731,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,10 +742,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -757,10 +753,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -768,10 +764,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -805,10 +801,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -816,10 +812,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -827,10 +823,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -862,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>3650</v>
@@ -873,7 +869,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -885,7 +881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C99E8B-6238-4FDC-AEB0-78A5C20AE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B8EC62-5960-45A3-86EA-C30F90735112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -61,24 +61,9 @@
     <t>EndDate__c</t>
   </si>
   <si>
-    <t>Automation Account</t>
-  </si>
-  <si>
-    <t>Automation Fund</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>Funding Source Description</t>
-  </si>
-  <si>
-    <t>Automation Runtime Funding Source</t>
-  </si>
-  <si>
-    <t>Automation Runtime Funding Account</t>
-  </si>
-  <si>
     <t>Automation Runtime External Funding Source</t>
   </si>
   <si>
@@ -103,9 +88,6 @@
     <t>CostCategory__c</t>
   </si>
   <si>
-    <t>Contractual</t>
-  </si>
-  <si>
     <t>Grant__c</t>
   </si>
   <si>
@@ -113,25 +95,34 @@
   </si>
   <si>
     <t>Automation Grantee Grant</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Department execution details</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Fund</t>
+  </si>
+  <si>
+    <t>Construction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="9"/>
@@ -186,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -195,8 +186,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -217,9 +207,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +247,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +353,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +495,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -539,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -594,7 +584,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
@@ -605,7 +595,7 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
@@ -643,10 +633,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -654,10 +644,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
         <v>11</v>
+      </c>
+      <c r="C3">
+        <v>10000000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -665,10 +655,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4">
-        <v>10000000</v>
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -701,7 +691,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C2">
@@ -712,7 +702,7 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
@@ -723,44 +713,44 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>18</v>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>19</v>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +787,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -805,10 +795,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -816,10 +806,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C99E8B-6238-4FDC-AEB0-78A5C20AE193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198A3084-AF20-49BB-BBD7-654B377EA392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="24">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -106,13 +106,7 @@
     <t>Contractual</t>
   </si>
   <si>
-    <t>Grant__c</t>
-  </si>
-  <si>
     <t>Type__c</t>
-  </si>
-  <si>
-    <t>Automation Grantee Grant</t>
   </si>
 </sst>
 </file>
@@ -217,9 +211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -514,13 +508,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,7 +547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -573,13 +567,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -601,7 +595,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -621,13 +615,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -649,7 +643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -660,7 +654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -680,13 +674,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -708,7 +702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -719,7 +713,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -730,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -741,7 +735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -752,7 +746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -771,14 +765,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,25 +794,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -830,12 +813,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -857,7 +840,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MergeOrg2_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198A3084-AF20-49BB-BBD7-654B377EA392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9E5FEF-6543-4977-9DB5-971FAACA20F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -508,13 +508,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -547,7 +547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -567,13 +567,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -643,7 +643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -654,7 +654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -674,13 +674,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -746,7 +746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -766,13 +766,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -783,7 +783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -794,7 +794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -813,12 +813,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -829,7 +829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -840,7 +840,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MergeOrg2_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9E5FEF-6543-4977-9DB5-971FAACA20F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9372832-2718-4735-9356-940A77BAFD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
